--- a/sheets/대금율보/검수/기다리는 마음.xlsx
+++ b/sheets/대금율보/검수/기다리는 마음.xlsx
@@ -3447,11 +3447,7 @@
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -3463,11 +3459,7 @@
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -3479,11 +3471,7 @@
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
@@ -3642,11 +3630,7 @@
           <t xml:space="preserve">렸</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -3658,11 +3642,7 @@
           <t xml:space="preserve">않</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
@@ -3674,11 +3654,7 @@
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
@@ -3690,11 +3666,7 @@
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">

--- a/sheets/대금율보/검수/기다리는 마음.xlsx
+++ b/sheets/대금율보/검수/기다리는 마음.xlsx
@@ -3247,28 +3247,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3775,7 +3775,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3989,6 +3989,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>